--- a/web/files/九龙-九龙塘-缇外.xlsx
+++ b/web/files/九龙-九龙塘-缇外.xlsx
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>4325</v>
+        <v>4218</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -3807,14 +3807,14 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
         <v>200000000</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>46243</v>
+        <v>47416</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -6103,10 +6103,10 @@
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>B | 4325呎 (4+房)
+          <t>B | 4218呎 (4+房)
 $20000万
-$46,243/呎
-(26年-09月-01日)</t>
+$47,416/呎
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>

--- a/web/files/九龙-九龙塘-缇外.xlsx
+++ b/web/files/九龙-九龙塘-缇外.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -127,6 +127,12 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -236,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -304,19 +310,22 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3394,7 +3403,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -3404,12 +3413,12 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -3419,12 +3428,12 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -3434,7 +3443,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4141,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>7403</v>
+        <v>7179</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -4141,14 +4150,14 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
         <v>580000000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>78347</v>
+        <v>80791</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -5928,27 +5937,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6038,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 4483呎 (4+房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -6268,10 +6277,10 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>PH A | 7403呎 (4+房)
+          <t>PH A | 7179呎 (4+房)
 $58000万
-$78,347/呎
-(26年-08月-30日)</t>
+$80,791/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -6472,32 +6481,32 @@
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>3 套</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="25" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>3 套</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>

--- a/web/files/九龙-九龙塘-缇外.xlsx
+++ b/web/files/九龙-九龙塘-缇外.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -127,12 +127,6 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -242,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -310,22 +304,19 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3403,23 +3394,19 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>260000000</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>57997</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3428,12 +3415,12 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -3443,7 +3430,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5924,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5947,7 +5934,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6038,12 +6025,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 4483呎 (4+房)
-招标单位
--
-(在售)</t>
+$26000万
+$57,997/呎
+(26年-10月-03日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -6481,32 +6468,32 @@
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>3 套</t>
         </is>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>3 套</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>

--- a/web/files/九龙-九龙塘-缇外.xlsx
+++ b/web/files/九龙-九龙塘-缇外.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -127,6 +127,12 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -236,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -304,19 +310,22 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3460,7 +3469,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -3470,12 +3479,12 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -3485,12 +3494,12 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -3500,7 +3509,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5924,27 +5933,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6017,12 +6026,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 4437呎 (4+房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -6468,32 +6477,32 @@
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>3 套</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="25" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>3 套</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>

--- a/web/files/九龙-九龙塘-缇外.xlsx
+++ b/web/files/九龙-九龙塘-缇外.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -127,12 +127,6 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -242,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -310,22 +304,19 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3399,7 +3390,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>4483</v>
+        <v>4378</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3408,14 +3399,14 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
         <v>260000000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>57997</v>
+        <v>59388</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3469,23 +3460,19 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>263800000</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>59455</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3494,12 +3481,12 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -3509,7 +3496,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5920,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5943,7 +5930,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6026,20 +6013,20 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 4437呎 (4+房)
-招标单位
--
-(在售)</t>
+$26380万
+$59,455/呎
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>B | 4483呎 (4+房)
+          <t>B | 4378呎 (4+房)
 $26000万
-$57,997/呎
-(26年-10月-03日)</t>
+$59,388/呎
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -6477,32 +6464,32 @@
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>3 套</t>
         </is>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>3 套</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>

--- a/web/files/九龙-九龙塘-缇外.xlsx
+++ b/web/files/九龙-九龙塘-缇外.xlsx
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>7912</v>
+        <v>8239</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>600000000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>75834</v>
+        <v>72824</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4247</v>
+        <v>4253</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>227500000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>53567</v>
+        <v>53492</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4247</v>
+        <v>4315</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>216000000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>50859</v>
+        <v>50058</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4335</v>
+        <v>4432</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>215000000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>49596</v>
+        <v>48511</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4247</v>
+        <v>4359</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>200000000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>47092</v>
+        <v>45882</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4269</v>
+        <v>4339</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>210000000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>49192</v>
+        <v>48398</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4395</v>
+        <v>4557</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>260000000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>59158</v>
+        <v>57055</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4258</v>
+        <v>4364</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>225000000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>52842</v>
+        <v>51558</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4395</v>
+        <v>4557</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>225000000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>51195</v>
+        <v>49375</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4258</v>
+        <v>4364</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>195000000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>45796</v>
+        <v>44684</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4395</v>
+        <v>4557</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>190000000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>43231</v>
+        <v>41694</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4099</v>
+        <v>4205</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>185000000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>45133</v>
+        <v>43995</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4236</v>
+        <v>4398</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>176800000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>41737</v>
+        <v>40200</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3955</v>
+        <v>4057</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>171000000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>43236</v>
+        <v>42149</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>8402</v>
+        <v>8564</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>600000000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>71412</v>
+        <v>70061</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4394</v>
+        <v>4451</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>250000000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>56896</v>
+        <v>56167</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4378</v>
+        <v>4483</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>255800000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>58429</v>
+        <v>57060</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4394</v>
+        <v>4557</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>220000000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>50068</v>
+        <v>48277</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4378</v>
+        <v>4483</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>230000000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>52535</v>
+        <v>51305</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4394</v>
+        <v>4557</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>192000000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>43696</v>
+        <v>42133</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4378</v>
+        <v>4483</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>192000000</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>43856</v>
+        <v>42828</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>4311</v>
+        <v>4431</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>208500000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>48365</v>
+        <v>47055</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>4072</v>
+        <v>4176</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>180000000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>44204</v>
+        <v>43103</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>8283</v>
+        <v>8444</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>580000000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>70023</v>
+        <v>68688</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>4378</v>
+        <v>4483</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>260000000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>59388</v>
+        <v>57997</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>4378</v>
+        <v>4483</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>230000000</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>52535</v>
+        <v>51305</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>4274</v>
+        <v>4437</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>230000000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>53814</v>
+        <v>51837</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>4274</v>
+        <v>4437</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>191800000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>44876</v>
+        <v>43227</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>4218</v>
+        <v>4325</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>200000000</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>47416</v>
+        <v>46243</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>4116</v>
+        <v>4278</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>185000000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>44947</v>
+        <v>43245</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>4074</v>
+        <v>4176</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>180000000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>44183</v>
+        <v>43103</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>4194</v>
+        <v>4311</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>185000000</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>44111</v>
+        <v>42913</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>7179</v>
+        <v>7403</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>580000000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>80791</v>
+        <v>78347</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>4260</v>
+        <v>4262</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>245000000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>57512</v>
+        <v>57485</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>4261</v>
+        <v>4332</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>225000000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>52805</v>
+        <v>51939</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>3701</v>
+        <v>3765</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>190000000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>51337</v>
+        <v>50465</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>4260</v>
+        <v>4390</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>215000000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>50469</v>
+        <v>48975</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>3728</v>
+        <v>3787</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>192000000</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>51502</v>
+        <v>50700</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>3723</v>
+        <v>3787</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>180000000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>48348</v>
+        <v>47531</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>3788</v>
+        <v>3855</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>170000000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>44879</v>
+        <v>44099</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>3410</v>
+        <v>3466</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>200000000</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>58651</v>
+        <v>57703</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>10692</v>
+        <v>11382</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>1028000000</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>96147</v>
+        <v>90318</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>11145</v>
+        <v>11692</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>1000000000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>89726</v>
+        <v>85529</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -5167,9 +5167,9 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>PH A | 7912呎 (4+房)
+          <t>PH A | 8239呎 (4+房)
 $60000万
-$75,834/呎
+$72,824/呎
 (24年-05月-09日)</t>
         </is>
       </c>
@@ -5190,9 +5190,9 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 4247呎 (4+房)
+          <t>A | 4253呎 (4+房)
 $22750万
-$53,567/呎
+$53,492/呎
 (25年-04月-30日)</t>
         </is>
       </c>
@@ -5215,9 +5215,9 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 4247呎 (4+房)
+          <t>A | 4315呎 (4+房)
 $21600万
-$50,859/呎
+$50,058/呎
 (24年-06月-20日)</t>
         </is>
       </c>
@@ -5240,17 +5240,17 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 4247呎 (4+房)
+          <t>A | 4359呎 (4+房)
 $20000万
-$47,092/呎
+$45,882/呎
 (26年-08月-17日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 4335呎 (4+房)
+          <t>B | 4432呎 (4+房)
 $21500万
-$49,596/呎
+$48,511/呎
 (26年-07月-23日)</t>
         </is>
       </c>
@@ -5265,9 +5265,9 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 4269呎 (4+房)
+          <t>A | 4339呎 (4+房)
 $21000万
-$49,192/呎
+$48,398/呎
 (26年-06月-29日)</t>
         </is>
       </c>
@@ -5459,9 +5459,9 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 4395呎 (4+房)
+          <t>A | 4557呎 (4+房)
 $26000万
-$59,158/呎
+$57,055/呎
 (24年-10月-07日)</t>
         </is>
       </c>
@@ -5483,17 +5483,17 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 4395呎 (4+房)
+          <t>A | 4557呎 (4+房)
 $22500万
-$51,195/呎
+$49,375/呎
 (24年-04月-16日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 4258呎 (4+房)
+          <t>B | 4364呎 (4+房)
 $22500万
-$52,842/呎
+$51,558/呎
 (24年-11月-15日)</t>
         </is>
       </c>
@@ -5507,17 +5507,17 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 4395呎 (4+房)
+          <t>A | 4557呎 (4+房)
 $19000万
-$43,231/呎
+$41,694/呎
 (26年-02月-04日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>B | 4258呎 (4+房)
+          <t>B | 4364呎 (4+房)
 $19500万
-$45,796/呎
+$44,684/呎
 (26年-02月-27日)</t>
         </is>
       </c>
@@ -5531,17 +5531,17 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 4236呎 (4+房)
+          <t>A | 4398呎 (4+房)
 $17680万
-$41,737/呎
+$40,200/呎
 (26年-01月-29日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>B | 4099呎 (4+房)
+          <t>B | 4205呎 (4+房)
 $18500万
-$45,133/呎
+$43,995/呎
 (25年-12月-22日)</t>
         </is>
       </c>
@@ -5563,9 +5563,9 @@
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>B | 3955呎 (4+房)
+          <t>B | 4057呎 (4+房)
 $17100万
-$43,236/呎
+$42,149/呎
 (24年-11月-04日)</t>
         </is>
       </c>
@@ -5698,9 +5698,9 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>PH | 8402呎 (4+房)
+          <t>PH | 8564呎 (4+房)
 $60000万
-$71,412/呎
+$70,061/呎
 (25年-10月-13日)</t>
         </is>
       </c>
@@ -5721,9 +5721,9 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 4394呎 (4+房)
+          <t>B | 4451呎 (4+房)
 $25000万
-$56,896/呎
+$56,167/呎
 (24年-07月-19日)</t>
         </is>
       </c>
@@ -5737,9 +5737,9 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 4378呎 (4+房)
+          <t>A | 4483呎 (4+房)
 $25580万
-$58,429/呎
+$57,060/呎
 (24年-06月-28日)</t>
         </is>
       </c>
@@ -5761,17 +5761,17 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 4378呎 (4+房)
+          <t>A | 4483呎 (4+房)
 $23000万
-$52,535/呎
+$51,305/呎
 (24年-08月-08日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 4394呎 (4+房)
+          <t>B | 4557呎 (4+房)
 $22000万
-$50,068/呎
+$48,277/呎
 (24年-09月-16日)</t>
         </is>
       </c>
@@ -5785,17 +5785,17 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 4378呎 (4+房)
+          <t>A | 4483呎 (4+房)
 $19200万
-$43,856/呎
+$42,828/呎
 (25年-12月-17日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>B | 4394呎 (4+房)
+          <t>B | 4557呎 (4+房)
 $19200万
-$43,696/呎
+$42,133/呎
 (24年-12月-06日)</t>
         </is>
       </c>
@@ -5833,17 +5833,17 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 4072呎 (4+房)
+          <t>A | 4176呎 (4+房)
 $18000万
-$44,204/呎
+$43,103/呎
 (24年-08月-06日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>B | 4311呎 (4+房)
+          <t>B | 4431呎 (4+房)
 $20850万
-$48,365/呎
+$47,055/呎
 (24年-09月-30日)</t>
         </is>
       </c>
@@ -5976,9 +5976,9 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>PH | 8283呎 (4+房)
+          <t>PH | 8444呎 (4+房)
 $58000万
-$70,023/呎
+$68,688/呎
 (25年-11月-06日)</t>
         </is>
       </c>
@@ -6023,9 +6023,9 @@
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>B | 4378呎 (4+房)
+          <t>B | 4483呎 (4+房)
 $26000万
-$59,388/呎
+$57,997/呎
 (26年-10月-22日)</t>
         </is>
       </c>
@@ -6039,17 +6039,17 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 4274呎 (4+房)
+          <t>A | 4437呎 (4+房)
 $23000万
-$53,814/呎
+$51,837/呎
 (25年-03月-21日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 4378呎 (4+房)
+          <t>B | 4483呎 (4+房)
 $23000万
-$52,535/呎
+$51,305/呎
 (26年-03月-27日)</t>
         </is>
       </c>
@@ -6063,9 +6063,9 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 4274呎 (4+房)
+          <t>A | 4437呎 (4+房)
 $19180万
-$44,876/呎
+$43,227/呎
 (24年-10月-10日)</t>
         </is>
       </c>
@@ -6087,17 +6087,17 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 4116呎 (4+房)
+          <t>A | 4278呎 (4+房)
 $18500万
-$44,947/呎
+$43,245/呎
 (25年-02月-24日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>B | 4218呎 (4+房)
+          <t>B | 4325呎 (4+房)
 $20000万
-$47,416/呎
+$46,243/呎
 (26年-09月-18日)</t>
         </is>
       </c>
@@ -6111,17 +6111,17 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 4194呎 (4+房)
+          <t>A | 4311呎 (4+房)
 $18500万
-$44,111/呎
+$42,913/呎
 (24年-10月-21日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>B | 4074呎 (4+房)
+          <t>B | 4176呎 (4+房)
 $18000万
-$44,183/呎
+$43,103/呎
 (24年-07月-23日)</t>
         </is>
       </c>
@@ -6260,9 +6260,9 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>PH A | 7179呎 (4+房)
+          <t>PH A | 7403呎 (4+房)
 $58000万
-$80,791/呎
+$78,347/呎
 (26年-09月-28日)</t>
         </is>
       </c>
@@ -6291,9 +6291,9 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 4260呎 (4+房)
+          <t>B | 4262呎 (4+房)
 $24500万
-$57,512/呎
+$57,485/呎
 (26年-07月-27日)</t>
         </is>
       </c>
@@ -6308,17 +6308,17 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 3701呎 (4+房)
+          <t>A | 3765呎 (4+房)
 $19000万
-$51,337/呎
+$50,465/呎
 (24年-06月-28日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>B | 4261呎 (4+房)
+          <t>B | 4332呎 (4+房)
 $22500万
-$52,805/呎
+$51,939/呎
 (25年-12月-22日)</t>
         </is>
       </c>
@@ -6333,17 +6333,17 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 3728呎 (4+房)
+          <t>A | 3787呎 (4+房)
 $19200万
-$51,502/呎
+$50,700/呎
 (24年-07月-25日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 4260呎 (4+房)
+          <t>B | 4390呎 (4+房)
 $21500万
-$50,469/呎
+$48,975/呎
 (26年-05月-22日)</t>
         </is>
       </c>
@@ -6358,9 +6358,9 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 3723呎 (4+房)
+          <t>A | 3787呎 (4+房)
 $18000万
-$48,348/呎
+$47,531/呎
 (24年-11月-29日)</t>
         </is>
       </c>
@@ -6383,17 +6383,17 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 3410呎 (4+房)
+          <t>A | 3466呎 (4+房)
 $20000万
-$58,651/呎
+$57,703/呎
 (26年-07月-27日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>B | 3788呎 (4+房)
+          <t>B | 3855呎 (4+房)
 $17000万
-$44,879/呎
+$44,099/呎
 (25年-09月-03日)</t>
         </is>
       </c>
@@ -6526,10 +6526,10 @@
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t>院墅A
-10692呎 (4+房)
+11382呎 (4+房)
 (24年-08月-28日)
 $10.28亿
-$96,147/呎</t>
+$90,318/呎</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -6544,10 +6544,10 @@
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t>院墅C
-11145呎 (4+房)
+11692呎 (4+房)
 (25年-05月-27日)
 $10.00亿
-$89,726/呎</t>
+$85,529/呎</t>
         </is>
       </c>
     </row>
